--- a/inputs/CEREBRO_Input_Template.xlsx
+++ b/inputs/CEREBRO_Input_Template.xlsx
@@ -33,8 +33,8 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <color rgb="00C9A84C"/>
+      <sz val="20"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -49,29 +49,29 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000D1B2A"/>
+      <color rgb="00060610"/>
       <sz val="12"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="000D1B2A"/>
+      <color rgb="00060610"/>
       <sz val="10"/>
     </font>
     <font>
-      <color rgb="000D1B2A"/>
+      <color rgb="00060610"/>
       <sz val="11"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00606060"/>
+      <color rgb="009CA3AF"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="009C0006"/>
+      <color rgb="00C62828"/>
       <sz val="9"/>
     </font>
     <font>
-      <color rgb="00606060"/>
+      <color rgb="009CA3AF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -85,7 +85,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00F4A261"/>
+      <color rgb="00C9A84C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -100,7 +100,7 @@
     </font>
     <font>
       <i val="1"/>
-      <color rgb="009C0006"/>
+      <color rgb="00C62828"/>
       <sz val="9"/>
     </font>
     <font>
@@ -109,7 +109,7 @@
       <sz val="12"/>
     </font>
     <font>
-      <color rgb="000D1B2A"/>
+      <color rgb="00060610"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -122,32 +122,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="000F2040"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002E86AB"/>
+        <fgColor rgb="000D6E6E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1B2A"/>
+        <fgColor rgb="00060610"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BDE0FE"/>
+        <fgColor rgb="00DCEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00F4F4F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF6E0"/>
+        <fgColor rgb="00F5EAC0"/>
       </patternFill>
     </fill>
     <fill>
@@ -176,10 +176,10 @@
     </border>
     <border>
       <top style="medium">
-        <color rgb="001F4E78"/>
+        <color rgb="000F2040"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E78"/>
+        <color rgb="000F2040"/>
       </bottom>
     </border>
     <border>
@@ -198,10 +198,10 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="001F4E78"/>
+        <color rgb="000F2040"/>
       </left>
       <right style="medium">
-        <color rgb="001F4E78"/>
+        <color rgb="000F2040"/>
       </right>
       <top style="thin">
         <color rgb="00888888"/>
@@ -218,24 +218,24 @@
         <color rgb="00888888"/>
       </right>
       <top style="medium">
-        <color rgb="001F4E78"/>
+        <color rgb="000F2040"/>
       </top>
       <bottom style="medium">
-        <color rgb="001F4E78"/>
+        <color rgb="000F2040"/>
       </bottom>
     </border>
     <border>
       <left style="dashed">
-        <color rgb="009C0006"/>
+        <color rgb="00C62828"/>
       </left>
       <right style="dashed">
-        <color rgb="009C0006"/>
+        <color rgb="00C62828"/>
       </right>
       <top style="dashed">
-        <color rgb="009C0006"/>
+        <color rgb="00C62828"/>
       </top>
       <bottom style="dashed">
-        <color rgb="009C0006"/>
+        <color rgb="00C62828"/>
       </bottom>
     </border>
   </borders>
@@ -411,12 +411,12 @@
     </comment>
     <comment ref="B6" authorId="0" shapeId="0">
       <text>
-        <t>One of: small_molecule, biologic, peptide. If left blank, the pipeline assumes small_molecule.</t>
+        <t>One of: small_molecule, biologic, peptide, oligonucleotide (also accepts aso, sirna, mirna, mrna, aptamer). If left blank, the pipeline assumes small_molecule. oligonucleotide is required for a raw DNA/RNA sequence -- without it, the letters are ambiguous with a short protein FASTA and will be analyzed as one.</t>
       </text>
     </comment>
     <comment ref="B7" authorId="0" shapeId="0">
       <text>
-        <t>Paste a SMILES string, a FASTA sequence (starting with '&gt;'), a 4-char PDB ID, or HELM peptide notation. If left blank, the pipeline tries to resolve from Drug Name.</t>
+        <t>Paste a SMILES string, a FASTA sequence (starting with '&gt;'), a 4-char PDB ID, HELM peptide notation, or a raw DNA/RNA sequence (set Molecule Class to oligonucleotide for this). If left blank, the pipeline tries to resolve from Drug Name.</t>
       </text>
     </comment>
     <comment ref="B15" authorId="0" shapeId="0">
@@ -777,10 +777,10 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CEREBRO-X Enterprise   ⟶   Drug Input</t>
+          <t>CEREBRO-X   ⟶   Drug Input</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>small_molecule | biologic | peptide</t>
+          <t>small_molecule | biologic | peptide | oligonucleotide</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -880,7 +880,7 @@
       <c r="B7" s="6" t="n"/>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>SMILES: COc1cc2c… | FASTA: &gt;seq\nMVLS… | PDB: 2NAO</t>
+          <t>SMILES: COc1cc2c… | FASTA: &gt;seq\nMVLS… | PDB: 2NAO | DNA/RNA: TCACTTTCATAATGCTGG</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
@@ -1259,7 +1259,7 @@
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>small_molecule | biologic | peptide</t>
+          <t>small_molecule | biologic | peptide | oligonucleotide</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -1277,7 +1277,7 @@
       <c r="B32" s="6" t="n"/>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>SMILES or sequence</t>
+          <t>SMILES, FASTA, or DNA/RNA sequence</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
@@ -1374,7 +1374,7 @@
       <c r="B38" s="6" t="n"/>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>small_molecule | biologic | peptide</t>
+          <t>small_molecule | biologic | peptide | oligonucleotide</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
@@ -1392,7 +1392,7 @@
       <c r="B39" s="6" t="n"/>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>SMILES or sequence</t>
+          <t>SMILES, FASTA, or DNA/RNA sequence</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
@@ -1476,19 +1476,19 @@
   </mergeCells>
   <dataValidations count="6">
     <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"small_molecule,biologic,peptide,monoclonal_antibody"</formula1>
+      <formula1>"small_molecule,biologic,peptide,monoclonal_antibody,oligonucleotide"</formula1>
     </dataValidation>
     <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"4,3,2,1,preclinical"</formula1>
     </dataValidation>
     <dataValidation sqref="B31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"small_molecule,biologic,peptide,monoclonal_antibody"</formula1>
+      <formula1>"small_molecule,biologic,peptide,monoclonal_antibody,oligonucleotide"</formula1>
     </dataValidation>
     <dataValidation sqref="B35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"4,3,2,1,preclinical"</formula1>
     </dataValidation>
     <dataValidation sqref="B38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"small_molecule,biologic,peptide,monoclonal_antibody"</formula1>
+      <formula1>"small_molecule,biologic,peptide,monoclonal_antibody,oligonucleotide"</formula1>
     </dataValidation>
     <dataValidation sqref="B42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"4,3,2,1,preclinical"</formula1>
@@ -1546,7 +1546,7 @@
     <col width="14" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CEREBRO-X   ⟶   DDS Formulations</t>
@@ -5461,7 +5461,7 @@
     <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CEREBRO-X   ⟶   How to Use This Workbook</t>
@@ -5613,7 +5613,7 @@
     <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>CEREBRO-X   ⟶   Material Science Library</t>
